--- a/dist/sample-bioneer-order.xlsx
+++ b/dist/sample-bioneer-order.xlsx
@@ -118,7 +118,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 nmole</t>
+          <t xml:space="preserve">50 nmole</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -145,7 +145,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 nmole</t>
+          <t xml:space="preserve">50 nmole</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
